--- a/ECO_STRUCT_Datos_31-08-2026.xlsx
+++ b/ECO_STRUCT_Datos_31-08-2026.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D30</f>
+        <f>'Mano de Obra'!D29</f>
         <v/>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17278,11 +17278,11 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 12, JOAQUIN</t>
+          <t>GARAJE MURCIA</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4043</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>20</v>
@@ -17295,18 +17295,18 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D30</f>
+        <f>D5/D29</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>PLAZA CIRCULAR</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>1963</v>
+        <v>437</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>20</v>
@@ -17319,18 +17319,18 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D30</f>
+        <f>D6/D29</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>LA ALBERCA</t>
+          <t>CEMENTERIO MURCIA</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1576</v>
+        <v>440</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>20</v>
@@ -17343,18 +17343,18 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D30</f>
+        <f>D7/D29</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>OBRA LUC2</t>
+          <t>LA PARTE DIFICIL, ALICANTE</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>1049</v>
+        <v>750</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
@@ -17367,18 +17367,18 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D30</f>
+        <f>D8/D29</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>A-13</t>
+          <t>LA PARTE DIFICIL, MURCIA</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>808</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
@@ -17391,18 +17391,18 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D30</f>
+        <f>D9/D29</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>LA PARTE DIFICIL, ALICANTE</t>
+          <t>A-13</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>750</v>
+        <v>808</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>20</v>
@@ -17415,18 +17415,18 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D30</f>
+        <f>D10/D29</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>LA PARTE DIFICIL, MURCIA</t>
+          <t>LA ALBERCA</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>51</v>
+        <v>1576</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>20</v>
@@ -17439,18 +17439,18 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D30</f>
+        <f>D11/D29</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>CARTAGENA, MURCIA</t>
+          <t>BARINAS</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>20</v>
@@ -17463,18 +17463,18 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D30</f>
+        <f>D12/D29</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 14, JUANMA</t>
+          <t>PLAZA CIRCULAR</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>643</v>
+        <v>1963</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>20</v>
@@ -17487,18 +17487,18 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D30</f>
+        <f>D13/D29</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>BARINAS</t>
+          <t>OBRA PADRE TRINI</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>537</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>20</v>
@@ -17511,18 +17511,18 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D30</f>
+        <f>D14/D29</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>CEMENTERIO, MURCIA</t>
+          <t>OBRA PISO IBI</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>440</v>
+        <v>117</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
@@ -17535,18 +17535,18 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D30</f>
+        <f>D15/D29</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>OBRA LUC2</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>437</v>
+        <v>1049</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>20</v>
@@ -17559,7 +17559,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D30</f>
+        <f>D16/D29</f>
         <v/>
       </c>
     </row>
@@ -17583,18 +17583,18 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D30</f>
+        <f>D17/D29</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>PEREAMAR</t>
+          <t>OBRA CALLE CARTAGENA, MURCIA</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>421</v>
+        <v>630</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>20</v>
@@ -17607,7 +17607,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D30</f>
+        <f>D18/D29</f>
         <v/>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D30</f>
+        <f>D19/D29</f>
         <v/>
       </c>
     </row>
@@ -17655,18 +17655,18 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D30</f>
+        <f>D20/D29</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>GARAJE MURCIA</t>
+          <t>FORMENTERA 14, JUANMA</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>132</v>
+        <v>643</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>20</v>
@@ -17679,18 +17679,18 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D30</f>
+        <f>D21/D29</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>PISO IBI</t>
+          <t>FORMENTERA 12, JOAQUIN</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>117</v>
+        <v>4043</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>20</v>
@@ -17703,18 +17703,18 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D30</f>
+        <f>D22/D29</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>OBRA PADRE TRINI</t>
+          <t>OBRA MADRE MARIA PEREAMAR</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>52</v>
+        <v>421</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>20</v>
@@ -17727,7 +17727,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D30</f>
+        <f>D23/D29</f>
         <v/>
       </c>
     </row>
@@ -17751,18 +17751,18 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D30</f>
+        <f>D24/D29</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
+          <t>LA ALBERCA</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>24</v>
+        <v>273</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>
@@ -17772,21 +17772,21 @@
         <v/>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D30</f>
+        <f>D25/D29</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 14, JUANMA</t>
+          <t>BARINAS</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3960</v>
+        <v>138</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>20</v>
@@ -17799,18 +17799,18 @@
         <v>2025</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D30</f>
+        <f>D26/D29</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 12, JOAQUIN</t>
+          <t>FORMENTERA 14, JUANMA</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>262</v>
+        <v>3960</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>20</v>
@@ -17823,18 +17823,18 @@
         <v>2025</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D30</f>
+        <f>D27/D29</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>LA ALBERCA</t>
+          <t>FORMENTERA 12, JOAQUIN</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>20</v>
@@ -17847,51 +17847,27 @@
         <v>2025</v>
       </c>
       <c r="F28" s="6">
-        <f>D28/D30</f>
+        <f>D28/D29</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>BARINAS</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D29" s="4">
-        <f>B29*C29</f>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="B29" s="7">
+        <f>SUM(B5:B28)</f>
         <v/>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F29" s="6">
-        <f>D29/D30</f>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8">
+        <f>SUM(D5:D28)</f>
         <v/>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL MANO DE OBRA</t>
-        </is>
-      </c>
-      <c r="B30" s="7">
-        <f>SUM(B5:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8">
-        <f>SUM(D5:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos_31-08-2026.xlsx
+++ b/ECO_STRUCT_Datos_31-08-2026.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>'Mano de Obra'!D29</f>
+        <f>'Mano de Obra'!D30</f>
         <v/>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -17295,7 +17295,7 @@
         <v>2026</v>
       </c>
       <c r="F5" s="6">
-        <f>D5/D29</f>
+        <f>D5/D30</f>
         <v/>
       </c>
     </row>
@@ -17319,7 +17319,7 @@
         <v>2026</v>
       </c>
       <c r="F6" s="6">
-        <f>D6/D29</f>
+        <f>D6/D30</f>
         <v/>
       </c>
     </row>
@@ -17343,7 +17343,7 @@
         <v>2026</v>
       </c>
       <c r="F7" s="6">
-        <f>D7/D29</f>
+        <f>D7/D30</f>
         <v/>
       </c>
     </row>
@@ -17367,7 +17367,7 @@
         <v>2026</v>
       </c>
       <c r="F8" s="6">
-        <f>D8/D29</f>
+        <f>D8/D30</f>
         <v/>
       </c>
     </row>
@@ -17391,7 +17391,7 @@
         <v>2026</v>
       </c>
       <c r="F9" s="6">
-        <f>D9/D29</f>
+        <f>D9/D30</f>
         <v/>
       </c>
     </row>
@@ -17415,7 +17415,7 @@
         <v>2026</v>
       </c>
       <c r="F10" s="6">
-        <f>D10/D29</f>
+        <f>D10/D30</f>
         <v/>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
         <v>2026</v>
       </c>
       <c r="F11" s="6">
-        <f>D11/D29</f>
+        <f>D11/D30</f>
         <v/>
       </c>
     </row>
@@ -17463,7 +17463,7 @@
         <v>2026</v>
       </c>
       <c r="F12" s="6">
-        <f>D12/D29</f>
+        <f>D12/D30</f>
         <v/>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
         <v>2026</v>
       </c>
       <c r="F13" s="6">
-        <f>D13/D29</f>
+        <f>D13/D30</f>
         <v/>
       </c>
     </row>
@@ -17511,7 +17511,7 @@
         <v>2026</v>
       </c>
       <c r="F14" s="6">
-        <f>D14/D29</f>
+        <f>D14/D30</f>
         <v/>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
         <v>2026</v>
       </c>
       <c r="F15" s="6">
-        <f>D15/D29</f>
+        <f>D15/D30</f>
         <v/>
       </c>
     </row>
@@ -17559,7 +17559,7 @@
         <v>2026</v>
       </c>
       <c r="F16" s="6">
-        <f>D16/D29</f>
+        <f>D16/D30</f>
         <v/>
       </c>
     </row>
@@ -17583,7 +17583,7 @@
         <v>2026</v>
       </c>
       <c r="F17" s="6">
-        <f>D17/D29</f>
+        <f>D17/D30</f>
         <v/>
       </c>
     </row>
@@ -17607,7 +17607,7 @@
         <v>2026</v>
       </c>
       <c r="F18" s="6">
-        <f>D18/D29</f>
+        <f>D18/D30</f>
         <v/>
       </c>
     </row>
@@ -17631,7 +17631,7 @@
         <v>2026</v>
       </c>
       <c r="F19" s="6">
-        <f>D19/D29</f>
+        <f>D19/D30</f>
         <v/>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
         <v>2026</v>
       </c>
       <c r="F20" s="6">
-        <f>D20/D29</f>
+        <f>D20/D30</f>
         <v/>
       </c>
     </row>
@@ -17679,7 +17679,7 @@
         <v>2026</v>
       </c>
       <c r="F21" s="6">
-        <f>D21/D29</f>
+        <f>D21/D30</f>
         <v/>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
         <v>2026</v>
       </c>
       <c r="F22" s="6">
-        <f>D22/D29</f>
+        <f>D22/D30</f>
         <v/>
       </c>
     </row>
@@ -17727,7 +17727,7 @@
         <v>2026</v>
       </c>
       <c r="F23" s="6">
-        <f>D23/D29</f>
+        <f>D23/D30</f>
         <v/>
       </c>
     </row>
@@ -17751,18 +17751,18 @@
         <v>2026</v>
       </c>
       <c r="F24" s="6">
-        <f>D24/D29</f>
+        <f>D24/D30</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>LA ALBERCA</t>
+          <t>OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>20</v>
@@ -17772,21 +17772,21 @@
         <v/>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F25" s="6">
-        <f>D25/D29</f>
+        <f>D25/D30</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>BARINAS</t>
+          <t>LA ALBERCA</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>20</v>
@@ -17796,21 +17796,21 @@
         <v/>
       </c>
       <c r="E26" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F26" s="6">
-        <f>D26/D29</f>
+        <f>D26/D30</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 14, JUANMA</t>
+          <t>BARINAS</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3960</v>
+        <v>138</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>20</v>
@@ -17820,21 +17820,21 @@
         <v/>
       </c>
       <c r="E27" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F27" s="6">
-        <f>D27/D29</f>
+        <f>D27/D30</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>FORMENTERA 12, JOAQUIN</t>
+          <t>FORMENTERA 14, JUANMA</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>262</v>
+        <v>3960</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>20</v>
@@ -17844,30 +17844,54 @@
         <v/>
       </c>
       <c r="E28" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F28" s="6">
-        <f>D28/D29</f>
+        <f>D28/D30</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>FORMENTERA 12, JOAQUIN</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="6">
+        <f>D29/D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>TOTAL MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(B5:B28)</f>
+      <c r="B30" s="7">
+        <f>SUM(B5:B29)</f>
         <v/>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8">
-        <f>SUM(D5:D28)</f>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8">
+        <f>SUM(D5:D29)</f>
         <v/>
       </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ECO_STRUCT_Datos_31-08-2026.xlsx
+++ b/ECO_STRUCT_Datos_31-08-2026.xlsx
@@ -17282,7 +17282,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>20</v>
